--- a/AAII_Financials/Quarterly/EPD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EPD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>EPD</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>18269000</v>
+      </c>
+      <c r="E8" s="3">
         <v>14386000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13793000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12023000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11363000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15417000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14201000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13775000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13483000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14760000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14622000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11998000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10651000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12444000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13650000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15468000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16060000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>13008000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11370200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10831300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9450100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9155300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7044200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6922000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5751000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7482500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8005300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7964100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8276300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8543500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9182300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9585900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8467500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>9298500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>8426600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6886900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>6607600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>7320400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>6478800</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>5920400</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>16056000</v>
+      </c>
+      <c r="E9" s="3">
         <v>12495000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11780000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10349000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9581000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13680000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12270000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12006000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11758000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12954000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12766000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10355000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9134000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10744000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>11062000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12856000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13452000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10624000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9191800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8624100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7346900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6761700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4891500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4797900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3689500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5305800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5811800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5743600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6072200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6286500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6856600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>7268300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6817200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>7534700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>7414300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>6079800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>5730200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>6333200</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>5608700</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>5065700</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2213000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1891000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2013000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1674000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1782000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1737000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1931000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1769000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1725000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1806000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1856000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1643000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1517000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1700000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2588000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2612000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2608000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2384000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2178400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2207200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2103200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2393600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2152700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2124100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2061500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2176700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2193500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2220500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2204100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2257000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2325700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2317600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1650300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1763800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1012300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>807100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>877400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>987200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>870100</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>854700</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,112 +1496,115 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E14" s="3">
         <v>8000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>9000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>18000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>11000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>10000</v>
+      </c>
+      <c r="J14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K14" s="3">
+        <v>28000</v>
+      </c>
+      <c r="L14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="M14" s="3">
+        <v>20000</v>
+      </c>
+      <c r="N14" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="O14" s="3">
+        <v>12000</v>
+      </c>
+      <c r="P14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="Q14" s="3">
         <v>13000</v>
       </c>
-      <c r="H14" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>28000</v>
-      </c>
-      <c r="K14" s="3">
-        <v>6000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>20000</v>
-      </c>
-      <c r="M14" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="N14" s="3">
-        <v>12000</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="R14" s="3">
         <v>5000</v>
       </c>
-      <c r="P14" s="3">
-        <v>13000</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
+        <v>29000</v>
+      </c>
+      <c r="T14" s="3">
         <v>5000</v>
       </c>
-      <c r="R14" s="3">
-        <v>29000</v>
-      </c>
-      <c r="S14" s="3">
-        <v>5000</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>14000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>119900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>29300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>17900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>65500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>800200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>77000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>11800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>81500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>39400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>7000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>4800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>29100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>4600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>13500</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-36100</v>
-      </c>
-      <c r="AK14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>8</v>
@@ -1601,53 +1621,56 @@
       <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>722000</v>
+      </c>
+      <c r="E15" s="3">
         <v>701000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>684000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>660000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>643000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>636000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>628000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>618000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>611000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>616000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>601000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>599000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>576000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>567000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16120000</v>
+      </c>
+      <c r="E17" s="3">
         <v>12559000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11842000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10410000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9649000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13740000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12330000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12067000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11815000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13020000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12823000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10414000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9190000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10801000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11885000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13756000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14296000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11342000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9966700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9318200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7957500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7460800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6336000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5539500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4314100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5975000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6587300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6489900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6716000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6917300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7541900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7942600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>7478700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8123000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>7347200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6007700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>5668900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>6288800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>5555600</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>5015400</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2149000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1827000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1951000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1613000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1714000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1677000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1871000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1708000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1668000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1740000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1799000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1584000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1461000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1643000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1765000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1712000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1764000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1666000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1403500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1513100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1492600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1694500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>708200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1382500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1436900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1507500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1418000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1474200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1560300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1626200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1640400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1643300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>988800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1175500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1079400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>879200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>938700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1031600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>923200</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>905000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-77000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-85000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-92000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-93000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-95000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-108000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-99000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-101000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-102000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-115000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-122000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-135000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-104000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>11000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3000</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-10000</v>
       </c>
       <c r="T20" s="3">
         <v>-10000</v>
       </c>
       <c r="U20" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="V20" s="3">
         <v>-12900</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-15800</v>
       </c>
       <c r="W20" s="3">
         <v>-15800</v>
       </c>
       <c r="X20" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-14600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-15900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-17200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-14300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-10700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-7900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-128600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-39500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-62200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-27500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-16500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-6100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-10500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-41000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-18700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-27500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-14000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2979000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2605000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2720000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2365000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2450000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2408000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2607000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2425000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2380000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2458000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2515000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2305000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2172000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2314000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2333000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2254000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2307000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2195000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1928800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2023600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2002800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2202300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1219100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1878700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1945300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2005800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1902700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1839200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2009400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2038500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2044000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2098000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1441000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1596000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1461000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1273100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1317700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1419900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1315400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1282600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>384000</v>
+      </c>
+      <c r="E22" s="3">
         <v>385000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>375000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>354000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>332000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>340000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>346000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>343000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>332000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>331000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>325000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>328000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>302000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>314000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>296000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>299000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>297000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>306000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>313300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>299100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>299600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>307300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>312100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>300400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>302100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>301000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>276500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>285400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>274600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>271300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>281900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>281200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>277100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>248400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>235500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>233800</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>236500</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>240600</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>238700</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>242800</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1868000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1518000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1659000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1342000</v>
       </c>
-      <c r="G23" s="3">
-        <v>1468000</v>
-      </c>
       <c r="H23" s="3">
+        <v>1470000</v>
+      </c>
+      <c r="I23" s="3">
         <v>1430000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1646000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1450000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1435000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1504000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1604000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1371000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1294000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1432000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1480000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1410000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1457000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1350000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1077300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1198200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1177200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1372600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>380200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1064900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1120500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1195800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1133600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1060200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1246200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1292700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1331000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1345600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>705600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>916600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>802900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>626700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>674700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>777000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>680000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>647900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E24" s="3">
         <v>22000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-4000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-13000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>24000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>19000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>21000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>22000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>13000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>28000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>18000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>17000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>19000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>12700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>16100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>31200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>10000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>14300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-19100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>59700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-179200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>8200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>15400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>9700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>12300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>25800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>11000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>18400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>5100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>5600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>5400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>8700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>6000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>10300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1856000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1496000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1663000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1355000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>1454000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1406000</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1636000</v>
+      </c>
+      <c r="K26" s="3">
+        <v>1431000</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1420000</v>
+      </c>
+      <c r="M26" s="3">
+        <v>1483000</v>
+      </c>
+      <c r="N26" s="3">
+        <v>1605000</v>
+      </c>
+      <c r="O26" s="3">
+        <v>1349000</v>
+      </c>
+      <c r="P26" s="3">
+        <v>1281000</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>1422000</v>
+      </c>
+      <c r="R26" s="3">
         <v>1452000</v>
       </c>
-      <c r="H26" s="3">
-        <v>1406000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1636000</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1431000</v>
-      </c>
-      <c r="K26" s="3">
-        <v>1420000</v>
-      </c>
-      <c r="L26" s="3">
-        <v>1483000</v>
-      </c>
-      <c r="M26" s="3">
-        <v>1605000</v>
-      </c>
-      <c r="N26" s="3">
-        <v>1349000</v>
-      </c>
-      <c r="O26" s="3">
-        <v>1281000</v>
-      </c>
-      <c r="P26" s="3">
-        <v>1422000</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>1452000</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1392000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1440000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1331000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1064600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1182100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1146000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1362600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>365900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1084000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1060800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1375000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1125400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1044800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1236500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1280400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1305200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1334600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>687200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>911500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>797300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>621300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>666000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>771000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>669700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>643100</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1823000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1467000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1631000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1325000</v>
       </c>
-      <c r="G27" s="3">
-        <v>1419000</v>
-      </c>
       <c r="H27" s="3">
+        <v>1421000</v>
+      </c>
+      <c r="I27" s="3">
         <v>1380000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1607000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1402000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1390000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1442000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1557000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1305000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1241000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1376000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1408000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1349000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1399000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1285000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1020400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1143900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1103400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1329400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>330200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1045100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1027200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1340200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1090500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1013100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1207300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1252700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1278700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1307000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>669200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>896000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>770100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>606900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>649700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>756700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>655600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>631400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E32" s="3">
         <v>77000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>85000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>92000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>93000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>95000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>108000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>99000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>101000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>102000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>115000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>122000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>135000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>104000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-11000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3000</v>
-      </c>
-      <c r="S32" s="3">
-        <v>10000</v>
       </c>
       <c r="T32" s="3">
         <v>10000</v>
       </c>
       <c r="U32" s="3">
+        <v>10000</v>
+      </c>
+      <c r="V32" s="3">
         <v>12900</v>
-      </c>
-      <c r="V32" s="3">
-        <v>15800</v>
       </c>
       <c r="W32" s="3">
         <v>15800</v>
       </c>
       <c r="X32" s="3">
+        <v>15800</v>
+      </c>
+      <c r="Y32" s="3">
         <v>14600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>15900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>17200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>14300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>10700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>7900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>128600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>39500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>62200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>27500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>16500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>6100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>10500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>41000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>18700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>27500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>14000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>4500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>14300</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1841000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1483000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1648000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1338000</v>
       </c>
-      <c r="G33" s="3">
-        <v>1434000</v>
-      </c>
       <c r="H33" s="3">
+        <v>1436000</v>
+      </c>
+      <c r="I33" s="3">
         <v>1394000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1623000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1417000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1404000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1457000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1571000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1318000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1253000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1390000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1408000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1349000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1399000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1285000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1020400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1143900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1103400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1329400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>330200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1045100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1027200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1340200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1090500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1013100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1207300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1252700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1278700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1307000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>669200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>896000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>770100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>606900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>649700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>756700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>655600</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>631400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1841000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1483000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1648000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1338000</v>
       </c>
-      <c r="G35" s="3">
-        <v>1434000</v>
-      </c>
       <c r="H35" s="3">
+        <v>1436000</v>
+      </c>
+      <c r="I35" s="3">
         <v>1394000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1623000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1417000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1404000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1457000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1571000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1318000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1253000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1390000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1408000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1349000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1399000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1285000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1020400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1143900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1103400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1329400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>330200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1045100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1027200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1340200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1090500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1013100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1207300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1252700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1278700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1307000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>669200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>896000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>770100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>606900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>649700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>756700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>655600</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>631400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E41" s="3">
         <v>191000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>969000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>206000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>870000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>220000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>583000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1434000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>138000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>283000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>180000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>171000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>183000</v>
-      </c>
-      <c r="P41" s="3">
-        <v>76000</v>
       </c>
       <c r="Q41" s="3">
         <v>76000</v>
       </c>
       <c r="R41" s="3">
+        <v>76000</v>
+      </c>
+      <c r="S41" s="3">
         <v>167000</v>
-      </c>
-      <c r="S41" s="3">
-        <v>231000</v>
       </c>
       <c r="T41" s="3">
         <v>231000</v>
       </c>
       <c r="U41" s="3">
+        <v>231000</v>
+      </c>
+      <c r="V41" s="3">
         <v>2819400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2213500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>404500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>229400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1059900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1032200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1298500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2025700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>334700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1207800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>107300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>99300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>344800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>30200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>57900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>102100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>32900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>28600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>62400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>63100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>57100</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4359,11 +4449,11 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>2000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -4454,871 +4544,895 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
-      <c r="AN42" s="3" t="s">
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>300</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9410000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8354000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6501000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7523000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7570000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7855000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9249000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8210000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8661000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7606000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7783000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6940000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6138000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6642000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6981000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6737000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8563000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9074000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7002800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6287400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5397000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5853400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4898400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3953400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3061800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3366200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4893700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4487500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3962700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4293200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3662600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4224500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4320300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4443500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4360200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3395400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2658700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3154400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3330600</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>2945800</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4666000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5234000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3884000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4160000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3969000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3233000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3955000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3319000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3356000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3257000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3352000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3345000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2497000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2195000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2554000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3173000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3234000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2652000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2681000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3095900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3346800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3703300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3303500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3192600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2024100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1538800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2091400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1644700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1586100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1680500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1522100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2335800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1729600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1699900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1609800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1983200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1604300</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1922000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1770500</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1762500</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>659000</v>
+      </c>
+      <c r="E45" s="3">
         <v>991000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>434000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>452000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>689000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>613000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>534000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>626000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>465000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>323000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>347000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>409000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>333000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>195000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>987000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1005000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>933000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1021000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>766200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1231600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1162900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>798000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>647600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>615100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>731900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>788400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>543100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>573800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>602800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>555600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>531200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1095400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>894800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>545500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>531300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>619600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>492900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>502700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1363700</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>973200</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15905000</v>
+      </c>
+      <c r="E46" s="3">
         <v>15677000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13360000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13237000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14160000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12763000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15133000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14385000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13453000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12093000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12248000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11432000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9704000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9687000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10598000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11082000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12961000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12978000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>13269400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12828400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10311200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10584100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9909400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8793300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7116300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7719100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7862900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7913800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6258900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6628600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6060700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7685900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7002600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>6791000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6506400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>6031100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4784500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>5641500</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>6528200</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>5741600</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2165000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2176000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2185000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2201000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2221000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2251000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2259000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2268000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2292000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2321000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2330000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2337000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2332000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2338000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2352000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2356000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2374000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2426000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2428400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2433400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2442700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2449800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2429200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2485400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2547400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2608500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2600200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2660900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2652100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2654300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2615100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2603400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2581500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2583400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2659400</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2660200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>2661300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2671400</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>2677300</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>2687200</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>53930000</v>
+      </c>
+      <c r="E48" s="3">
         <v>52163000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>51812000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>51903000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>50908000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>50144000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>49062000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>48508000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>47862000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>46812000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>45804000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>45715000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>45419000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>44962000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>44766000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>44536000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>44494000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>44401000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>42433300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>42606700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>42551400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>42427000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>42244800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>42701200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>42887500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>42518000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>41813600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>40982800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>40316700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>39583800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>38737600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>37802900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>37054500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>36416300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>35620400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>34979300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>34220700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>33556100</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>33292500</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>33119400</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9763000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9815000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9871000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9919000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9614000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9665000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9717000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9227000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9279000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9328000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9378000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9429000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9479000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9527000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9573000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9618000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9664000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9709000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8599500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8638900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8678600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8708700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8758000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9093800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9124600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9154600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9194200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9234600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>9277800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>9311100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>9353600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>9399400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>9441300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>9481600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>9435500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>9485000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>9527600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>9568300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>9609300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>9652400</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3">
         <v>728000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>674000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>562000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>539000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>583000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>997000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>674000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>675000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>819000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1222000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>891000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>795000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>811000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>819000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>845000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>857000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>805000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>795000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>812500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>821200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>813900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>765300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>662500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>268700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>265100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>262300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>223200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>216300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>219700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>202800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>260600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>231500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>210000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>196400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>145000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>119200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>92200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>86700</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>57800</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>81758000</v>
+      </c>
+      <c r="E54" s="3">
         <v>80559000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>77902000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>77822000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>77442000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>75406000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>77168000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>75062000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>73561000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>71373000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>70982000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>69804000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>67729000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>67325000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>68108000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>68437000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>70350000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>70319000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>67525600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>67319900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>64805100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>64983500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>64106700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>63736200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>61944500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>62265300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>61733200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>61015300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>58721800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>58397500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>56969800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>57752200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>56311400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>55482300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>54418100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>53300600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>51313300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>51529500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>52194000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>51258400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1297000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1021000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1359000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1326000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1334000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1227000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1203000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1147000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1372000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1195000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>962000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>999000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>750000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>975000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>909000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>935000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>930000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>798600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>832800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>950400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>915800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>854100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1017300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>991800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>985200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1166800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1183300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1152100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1004700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1243000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1289400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>978700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>813600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>929000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>829300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>737300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>576200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>502800</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>551400</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2133000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2803000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1722000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2561000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1725000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2559000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1150000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1244000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2144000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1232000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1331000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1543000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1269000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1211000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1744000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2654000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1889000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2629000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1399800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1399300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1398900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1513400</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>1325000</v>
       </c>
       <c r="Z58" s="3">
         <v>1325000</v>
       </c>
       <c r="AA58" s="3">
+        <v>1325000</v>
+      </c>
+      <c r="AB58" s="3">
         <v>2325000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1750000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1981900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2300000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>500000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2694600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1500100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3405500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2668700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2376800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2855000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3009000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>3354800</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>2300000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>2576800</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>2838100</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1452000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1651000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1340000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1310000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1465000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1297000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1487000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1468000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1172000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>875000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1239000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1273000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>987000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>799000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9546000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9334000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12154000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11815000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9426100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9638600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8179300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8109700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6808900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5504600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4165600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4180200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5981000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5186200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4612000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4893400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4424400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6227400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>5801900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>5649200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>5511100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4600400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3726500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>4171800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>5170900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>4178800</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17152000</v>
+      </c>
+      <c r="E60" s="3">
         <v>17222000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12832000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15050000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14757000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14872000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15177000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13404000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14809000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13030000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13131000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12475000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10709000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10410000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12265000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12897000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14978000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>15374000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11624500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11870700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10528600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10538900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8988000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7846900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7482400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6915400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9129700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8669500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6264100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8592700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7167500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>10922300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>9449300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>8839600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>9295100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>8438700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>7818600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>7048000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>8250500</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>7568300</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>32077000</v>
+      </c>
+      <c r="E61" s="3">
         <v>31577000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>33160000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>31443000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>31454000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>29486000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>31112000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>31106000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>28655000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>28618000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27771000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27784000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>27778000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>27777000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>26551000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>26548000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>26892000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>26889000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>28135300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>28132800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>27148600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>27145900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>28540700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>28537000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>27285200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>27855900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>25643200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>25639200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>26385000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>24181600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>24678100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>22508500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>23020200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>23016400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>21713700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>21710900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>20026500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>21123000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>21120900</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>21121200</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>701000</v>
+      </c>
+      <c r="E62" s="3">
         <v>379000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>333000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>321000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>330000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>289000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>300000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>424000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>341000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>285000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>335000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>354000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>273000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>284000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1541000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1503000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1454000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1350000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1278000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1282500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1231800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1179200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1151300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1198500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1235500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1379800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1132800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1181100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1097300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1101900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>832000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>815600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>751400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>661400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>636900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>602100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>588000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>558500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>556600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>530200</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>50650000</v>
+      </c>
+      <c r="E66" s="3">
         <v>50168000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>47288000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47722000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>47473000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>45581000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>47529000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45854000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>44715000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>42847000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>42174000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>41533000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>39658000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>39417000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>41436000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>42040000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>44418000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>44717000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>42147400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>42349400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>39983000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>39941900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>39753300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>38651800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>37067800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>37214900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>36969200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>36519300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>34282000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>34339600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>33116300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>34679100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>33639800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>32729000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>31870900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>30970000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>28653200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>28950200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>30147000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>29439200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7535,7 +7703,7 @@
         <v>44000</v>
       </c>
       <c r="F70" s="3">
-        <v>50000</v>
+        <v>44000</v>
       </c>
       <c r="G70" s="3">
         <v>50000</v>
@@ -7550,7 +7718,7 @@
         <v>50000</v>
       </c>
       <c r="K70" s="3">
-        <v>49000</v>
+        <v>50000</v>
       </c>
       <c r="L70" s="3">
         <v>49000</v>
@@ -7580,7 +7748,7 @@
         <v>49000</v>
       </c>
       <c r="U70" s="3">
-        <v>49300</v>
+        <v>49000</v>
       </c>
       <c r="V70" s="3">
         <v>49300</v>
@@ -7595,11 +7763,11 @@
         <v>49300</v>
       </c>
       <c r="Z70" s="3">
+        <v>49300</v>
+      </c>
+      <c r="AA70" s="3">
         <v>49100</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,8 +7938,11 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7811,8 +7985,8 @@
       <c r="P72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
+      <c r="Q72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R72" s="3">
         <v>0</v>
@@ -7889,8 +8063,11 @@
       <c r="AP72" s="3">
         <v>0</v>
       </c>
+      <c r="AQ72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30248000</v>
+      </c>
+      <c r="E76" s="3">
         <v>29526000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>29739000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>29209000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>29066000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>28915000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>28732000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>28349000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>27989000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>27677000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>27673000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>27150000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>26951000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>26787000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>26623000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>26348000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>25883000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>25553000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>25328900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>24921200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>24772800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>24992300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>24304100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>25035300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>24876700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>25050400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>24764000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>24496000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>24439800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>24057900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>23853500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>23073100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>22671600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>22753300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>22547200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>22330600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>22660100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>22579300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>22047000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>21819200</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1841000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1483000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1648000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1338000</v>
       </c>
-      <c r="G81" s="3">
-        <v>1434000</v>
-      </c>
       <c r="H81" s="3">
+        <v>1436000</v>
+      </c>
+      <c r="I81" s="3">
         <v>1394000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1623000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1417000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1404000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1457000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1571000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1318000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1253000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1390000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1408000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1349000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1399000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1285000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1020400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1143900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1103400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1329400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>330200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1045100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1027200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1340200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1090500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1013100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1207300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1252700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1278700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1307000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>669200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>896000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>770100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>606900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>649700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>756700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>655600</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>631400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>624000</v>
+      </c>
+      <c r="E83" s="3">
         <v>607000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>598000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>586000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>601000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>563000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>558000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>572000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>540000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>533000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>530000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>529000</v>
       </c>
       <c r="O83" s="3">
         <v>529000</v>
       </c>
       <c r="P83" s="3">
+        <v>529000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>521000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>512000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>499000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>508000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>498000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>500600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>486600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>488500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>486300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>526800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>513400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>522700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>509000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>492600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>493600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>488600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>474500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>431100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>471200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>458300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>431000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>422600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>412600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>406500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>402300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>396700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>391900</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3181000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1469000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2472000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1738000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2061000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2314000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2358000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2072000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1574000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2111000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2366000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1718000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1902000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1583000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2725000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1050000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2119000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2145000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2125200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2370300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1993900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2023100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1599900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1097800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1181600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2012200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1694300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1642500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2023300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1160400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1851000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1577500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1464200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1233600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1846400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>485000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1459300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>875600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1407800</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>813800</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1158000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-983000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1301000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1958000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1299000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1062000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1059000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1174000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1264000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1047000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1012000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-821000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-780000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-653000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-761000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-472000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-382000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-349000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-417500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-504500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-622200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-679000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-616300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-695700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-896400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1079500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1229600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1041300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1111900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1148900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1219000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1083100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-974600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-946500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-983600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1005100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-682700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-876400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-3606300</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-563500</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1154000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-381000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1235000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1935000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1274000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1047000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2000000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1152000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1243000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1038000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-977000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-818000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-765000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-637000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-645000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-441000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-336000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3532000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-413100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-492800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-571700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-657000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-556500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-633700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-858800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1071700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1202700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1086300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1112000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1174500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1098800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1093200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-970500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1119100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1269900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1036700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-845300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-134200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-310100</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1457100</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1190000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1189000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1179000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1180000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1160000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1159000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1138000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1139000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1118000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>1117000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>1086000</v>
       </c>
       <c r="N96" s="3">
         <v>1086000</v>
       </c>
       <c r="O96" s="3">
+        <v>1086000</v>
+      </c>
+      <c r="P96" s="3">
         <v>1065000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>1064000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1034000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1035000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1014000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1012000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-981900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-983500</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-983300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-981700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-971400</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-972700</v>
       </c>
       <c r="AA96" s="3">
         <v>-972700</v>
       </c>
       <c r="AB96" s="3">
+        <v>-972700</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-974200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-968700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-963200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-957500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-950400</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-944000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-935600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-928800</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-918500</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-909500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-902600</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-888800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-869000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-852200</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-837800</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2076000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1939000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-424000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-467000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-145000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1651000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1193000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>319000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-281000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1009000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1383000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-863000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1136000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-876000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2129000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-751000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1839000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1125000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1105500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-130400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1145600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2189800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1016400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-769600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1001800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>765100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1289400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>544300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-911500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-288500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-621200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-546700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-367800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>30800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-893600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>556000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-647800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-742100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-753100</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>586900</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-851000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>813000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-664000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>642000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-384000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-835000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1239000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>50000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>64000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>37000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>70000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-49000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-142000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-56000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2512000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>606600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1747100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>276600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-823700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>27000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-305500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-679000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1705600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-797800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1100500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-302600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>131000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-62400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>125900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>145300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-317100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>4300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-33800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>344600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-56400</v>
       </c>
     </row>
